--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -459,7 +459,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -491,7 +491,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -571,7 +571,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -603,7 +603,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -52,10 +52,10 @@
     <t>COLIMA</t>
   </si>
   <si>
+    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+  </si>
+  <si>
     <t>OAXACA</t>
-  </si>
-  <si>
-    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
     <t>MORELOS</t>
@@ -547,7 +547,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -22,10 +22,10 @@
     <t>clues_faltantes</t>
   </si>
   <si>
+    <t>CIUDAD DE MEXICO</t>
+  </si>
+  <si>
     <t>GUERRERO</t>
-  </si>
-  <si>
-    <t>CIUDAD DE MEXICO</t>
   </si>
   <si>
     <t>SONORA</t>
@@ -459,7 +459,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -467,7 +467,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -587,7 +587,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -603,7 +603,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -523,7 +523,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -571,7 +571,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -40,10 +40,10 @@
     <t>BAJA CALIFORNIA</t>
   </si>
   <si>
+    <t>BAJA CALIFORNIA SUR</t>
+  </si>
+  <si>
     <t>MEXICO</t>
-  </si>
-  <si>
-    <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
     <t>QUINTANA ROO</t>
@@ -467,7 +467,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -515,7 +515,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -571,7 +571,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -603,7 +603,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -611,7 +611,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -467,7 +467,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -515,7 +515,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -571,7 +571,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -515,7 +515,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -611,7 +611,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -64,16 +64,16 @@
     <t>HIDALGO</t>
   </si>
   <si>
+    <t>PUEBLA</t>
+  </si>
+  <si>
+    <t>CAMPECHE</t>
+  </si>
+  <si>
     <t>NAYARIT</t>
   </si>
   <si>
-    <t>PUEBLA</t>
-  </si>
-  <si>
     <t>SINALOA</t>
-  </si>
-  <si>
-    <t>CAMPECHE</t>
   </si>
   <si>
     <t>MICHOACAN DE OCAMPO</t>
@@ -483,7 +483,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -579,7 +579,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -595,7 +595,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -563,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -563,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -55,10 +55,10 @@
     <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
+    <t>MORELOS</t>
+  </si>
+  <si>
     <t>OAXACA</t>
-  </si>
-  <si>
-    <t>MORELOS</t>
   </si>
   <si>
     <t>HIDALGO</t>
@@ -467,7 +467,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -491,7 +491,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -523,7 +523,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -531,7 +531,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -555,7 +555,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -611,7 +611,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -467,7 +467,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -491,7 +491,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -491,7 +491,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -587,7 +587,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -70,10 +70,10 @@
     <t>CAMPECHE</t>
   </si>
   <si>
+    <t>SINALOA</t>
+  </si>
+  <si>
     <t>NAYARIT</t>
-  </si>
-  <si>
-    <t>SINALOA</t>
   </si>
   <si>
     <t>MICHOACAN DE OCAMPO</t>
@@ -491,7 +491,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -515,7 +515,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -587,7 +587,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -595,7 +595,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -603,7 +603,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -491,7 +491,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -507,7 +507,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -595,7 +595,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -603,7 +603,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -507,7 +507,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -40,15 +40,15 @@
     <t>BAJA CALIFORNIA</t>
   </si>
   <si>
+    <t>MEXICO</t>
+  </si>
+  <si>
+    <t>QUINTANA ROO</t>
+  </si>
+  <si>
     <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
-    <t>MEXICO</t>
-  </si>
-  <si>
-    <t>QUINTANA ROO</t>
-  </si>
-  <si>
     <t>COLIMA</t>
   </si>
   <si>
@@ -70,10 +70,10 @@
     <t>CAMPECHE</t>
   </si>
   <si>
+    <t>NAYARIT</t>
+  </si>
+  <si>
     <t>SINALOA</t>
-  </si>
-  <si>
-    <t>NAYARIT</t>
   </si>
   <si>
     <t>MICHOACAN DE OCAMPO</t>
@@ -483,7 +483,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -491,7 +491,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -507,7 +507,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -515,7 +515,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -523,7 +523,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -531,7 +531,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -563,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -587,7 +587,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -595,7 +595,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -563,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -595,7 +595,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -563,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -61,22 +61,22 @@
     <t>OAXACA</t>
   </si>
   <si>
+    <t>PUEBLA</t>
+  </si>
+  <si>
     <t>HIDALGO</t>
   </si>
   <si>
-    <t>PUEBLA</t>
-  </si>
-  <si>
     <t>CAMPECHE</t>
   </si>
   <si>
     <t>NAYARIT</t>
   </si>
   <si>
+    <t>MICHOACAN DE OCAMPO</t>
+  </si>
+  <si>
     <t>SINALOA</t>
-  </si>
-  <si>
-    <t>MICHOACAN DE OCAMPO</t>
   </si>
   <si>
     <t>CHIAPAS</t>
@@ -483,7 +483,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>111</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -563,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -595,7 +595,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -64,10 +64,10 @@
     <t>PUEBLA</t>
   </si>
   <si>
+    <t>CAMPECHE</t>
+  </si>
+  <si>
     <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>CAMPECHE</t>
   </si>
   <si>
     <t>NAYARIT</t>
@@ -483,7 +483,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -571,7 +571,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -579,7 +579,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -483,7 +483,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -67,10 +67,10 @@
     <t>CAMPECHE</t>
   </si>
   <si>
+    <t>NAYARIT</t>
+  </si>
+  <si>
     <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>NAYARIT</t>
   </si>
   <si>
     <t>MICHOACAN DE OCAMPO</t>
@@ -483,7 +483,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -523,7 +523,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -579,7 +579,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -587,7 +587,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -49,16 +49,16 @@
     <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
+    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+  </si>
+  <si>
+    <t>MORELOS</t>
+  </si>
+  <si>
+    <t>OAXACA</t>
+  </si>
+  <si>
     <t>COLIMA</t>
-  </si>
-  <si>
-    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
-  </si>
-  <si>
-    <t>MORELOS</t>
-  </si>
-  <si>
-    <t>OAXACA</t>
   </si>
   <si>
     <t>PUEBLA</t>
@@ -483,7 +483,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -523,7 +523,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -531,7 +531,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -539,7 +539,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -547,7 +547,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -555,7 +555,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -49,10 +49,10 @@
     <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
+    <t>MORELOS</t>
+  </si>
+  <si>
     <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
-  </si>
-  <si>
-    <t>MORELOS</t>
   </si>
   <si>
     <t>OAXACA</t>
@@ -491,7 +491,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -523,7 +523,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -531,7 +531,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -603,7 +603,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -40,10 +40,10 @@
     <t>BAJA CALIFORNIA</t>
   </si>
   <si>
+    <t>QUINTANA ROO</t>
+  </si>
+  <si>
     <t>MEXICO</t>
-  </si>
-  <si>
-    <t>QUINTANA ROO</t>
   </si>
   <si>
     <t>BAJA CALIFORNIA SUR</t>
@@ -507,7 +507,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -515,7 +515,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -587,7 +587,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -43,21 +43,21 @@
     <t>QUINTANA ROO</t>
   </si>
   <si>
+    <t>BAJA CALIFORNIA SUR</t>
+  </si>
+  <si>
+    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+  </si>
+  <si>
+    <t>MORELOS</t>
+  </si>
+  <si>
+    <t>OAXACA</t>
+  </si>
+  <si>
     <t>MEXICO</t>
   </si>
   <si>
-    <t>BAJA CALIFORNIA SUR</t>
-  </si>
-  <si>
-    <t>MORELOS</t>
-  </si>
-  <si>
-    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
-  </si>
-  <si>
-    <t>OAXACA</t>
-  </si>
-  <si>
     <t>COLIMA</t>
   </si>
   <si>
@@ -70,10 +70,10 @@
     <t>NAYARIT</t>
   </si>
   <si>
+    <t>MICHOACAN DE OCAMPO</t>
+  </si>
+  <si>
     <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>MICHOACAN DE OCAMPO</t>
   </si>
   <si>
     <t>SINALOA</t>
@@ -515,7 +515,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -523,7 +523,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -539,7 +539,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -547,7 +547,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -595,7 +595,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -603,7 +603,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -55,16 +55,16 @@
     <t>OAXACA</t>
   </si>
   <si>
+    <t>COLIMA</t>
+  </si>
+  <si>
+    <t>PUEBLA</t>
+  </si>
+  <si>
+    <t>CAMPECHE</t>
+  </si>
+  <si>
     <t>MEXICO</t>
-  </si>
-  <si>
-    <t>COLIMA</t>
-  </si>
-  <si>
-    <t>PUEBLA</t>
-  </si>
-  <si>
-    <t>CAMPECHE</t>
   </si>
   <si>
     <t>NAYARIT</t>
@@ -547,7 +547,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -555,7 +555,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -563,7 +563,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -571,7 +571,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -595,7 +595,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -603,7 +603,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -64,25 +64,25 @@
     <t>CAMPECHE</t>
   </si>
   <si>
+    <t>NAYARIT</t>
+  </si>
+  <si>
     <t>MEXICO</t>
   </si>
   <si>
-    <t>NAYARIT</t>
-  </si>
-  <si>
     <t>MICHOACAN DE OCAMPO</t>
   </si>
   <si>
     <t>HIDALGO</t>
   </si>
   <si>
+    <t>CHIAPAS</t>
+  </si>
+  <si>
+    <t>SAN LUIS POTOSI</t>
+  </si>
+  <si>
     <t>SINALOA</t>
-  </si>
-  <si>
-    <t>CHIAPAS</t>
-  </si>
-  <si>
-    <t>SAN LUIS POTOSI</t>
   </si>
   <si>
     <t>ZACATECAS</t>
@@ -483,7 +483,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -515,7 +515,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -571,7 +571,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -579,7 +579,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -595,7 +595,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -603,7 +603,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -67,16 +67,16 @@
     <t>NAYARIT</t>
   </si>
   <si>
+    <t>MICHOACAN DE OCAMPO</t>
+  </si>
+  <si>
     <t>MEXICO</t>
   </si>
   <si>
-    <t>MICHOACAN DE OCAMPO</t>
+    <t>CHIAPAS</t>
   </si>
   <si>
     <t>HIDALGO</t>
-  </si>
-  <si>
-    <t>CHIAPAS</t>
   </si>
   <si>
     <t>SAN LUIS POTOSI</t>
@@ -515,7 +515,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -571,7 +571,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -587,7 +587,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -595,7 +595,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>entidad</t>
   </si>
@@ -46,12 +46,12 @@
     <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
+    <t>MORELOS</t>
+  </si>
+  <si>
     <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
-    <t>MORELOS</t>
-  </si>
-  <si>
     <t>OAXACA</t>
   </si>
   <si>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>NAYARIT</t>
-  </si>
-  <si>
-    <t>MICHOACAN DE OCAMPO</t>
   </si>
   <si>
     <t>MEXICO</t>
@@ -443,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -515,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -579,7 +576,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -587,7 +584,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -619,14 +616,6 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23">
         <v>1</v>
       </c>
     </row>

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -576,7 +576,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -512,7 +512,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -46,10 +46,10 @@
     <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
+    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+  </si>
+  <si>
     <t>MORELOS</t>
-  </si>
-  <si>
-    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
     <t>OAXACA</t>
@@ -528,7 +528,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -67,10 +67,10 @@
     <t>NAYARIT</t>
   </si>
   <si>
+    <t>CHIAPAS</t>
+  </si>
+  <si>
     <t>MEXICO</t>
-  </si>
-  <si>
-    <t>CHIAPAS</t>
   </si>
   <si>
     <t>HIDALGO</t>
@@ -576,7 +576,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -528,7 +528,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -49,10 +49,10 @@
     <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
+    <t>OAXACA</t>
+  </si>
+  <si>
     <t>MORELOS</t>
-  </si>
-  <si>
-    <t>OAXACA</t>
   </si>
   <si>
     <t>COLIMA</t>
@@ -528,7 +528,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>entidad</t>
   </si>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>CHIAPAS</t>
-  </si>
-  <si>
-    <t>MEXICO</t>
   </si>
   <si>
     <t>HIDALGO</t>
@@ -440,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -536,7 +533,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -608,14 +605,6 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22">
         <v>1</v>
       </c>
     </row>

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -533,7 +533,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -52,10 +52,10 @@
     <t>OAXACA</t>
   </si>
   <si>
+    <t>COLIMA</t>
+  </si>
+  <si>
     <t>MORELOS</t>
-  </si>
-  <si>
-    <t>COLIMA</t>
   </si>
   <si>
     <t>PUEBLA</t>
@@ -533,7 +533,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -541,7 +541,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -55,13 +55,13 @@
     <t>COLIMA</t>
   </si>
   <si>
+    <t>PUEBLA</t>
+  </si>
+  <si>
+    <t>CAMPECHE</t>
+  </si>
+  <si>
     <t>MORELOS</t>
-  </si>
-  <si>
-    <t>PUEBLA</t>
-  </si>
-  <si>
-    <t>CAMPECHE</t>
   </si>
   <si>
     <t>NAYARIT</t>
@@ -525,7 +525,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -541,7 +541,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -549,7 +549,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -557,7 +557,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>entidad</t>
   </si>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>CHIAPAS</t>
-  </si>
-  <si>
-    <t>HIDALGO</t>
   </si>
   <si>
     <t>SAN LUIS POTOSI</t>
@@ -437,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -477,7 +474,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -597,14 +594,6 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21">
         <v>1</v>
       </c>
     </row>

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -458,7 +458,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -55,10 +55,10 @@
     <t>COLIMA</t>
   </si>
   <si>
+    <t>CAMPECHE</t>
+  </si>
+  <si>
     <t>PUEBLA</t>
-  </si>
-  <si>
-    <t>CAMPECHE</t>
   </si>
   <si>
     <t>MORELOS</t>
@@ -538,7 +538,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -474,7 +474,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -506,7 +506,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>entidad</t>
   </si>
@@ -55,12 +55,12 @@
     <t>COLIMA</t>
   </si>
   <si>
+    <t>PUEBLA</t>
+  </si>
+  <si>
     <t>CAMPECHE</t>
   </si>
   <si>
-    <t>PUEBLA</t>
-  </si>
-  <si>
     <t>MORELOS</t>
   </si>
   <si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>SAN LUIS POTOSI</t>
-  </si>
-  <si>
-    <t>SINALOA</t>
   </si>
   <si>
     <t>ZACATECAS</t>
@@ -434,7 +431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -466,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -490,7 +487,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -506,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -586,14 +583,6 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20">
         <v>1</v>
       </c>
     </row>

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -503,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -31,22 +31,22 @@
     <t>SONORA</t>
   </si>
   <si>
+    <t>TAMAULIPAS</t>
+  </si>
+  <si>
+    <t>BAJA CALIFORNIA</t>
+  </si>
+  <si>
     <t>TABASCO</t>
   </si>
   <si>
-    <t>TAMAULIPAS</t>
-  </si>
-  <si>
-    <t>BAJA CALIFORNIA</t>
-  </si>
-  <si>
     <t>QUINTANA ROO</t>
   </si>
   <si>
+    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+  </si>
+  <si>
     <t>BAJA CALIFORNIA SUR</t>
-  </si>
-  <si>
-    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
     <t>OAXACA</t>
@@ -471,7 +471,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -479,7 +479,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -487,7 +487,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -511,7 +511,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -543,7 +543,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -487,7 +487,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -487,7 +487,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -46,10 +46,10 @@
     <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
+    <t>OAXACA</t>
+  </si>
+  <si>
     <t>BAJA CALIFORNIA SUR</t>
-  </si>
-  <si>
-    <t>OAXACA</t>
   </si>
   <si>
     <t>COLIMA</t>
@@ -487,7 +487,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -511,7 +511,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -519,7 +519,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -37,10 +37,10 @@
     <t>BAJA CALIFORNIA</t>
   </si>
   <si>
+    <t>QUINTANA ROO</t>
+  </si>
+  <si>
     <t>TABASCO</t>
-  </si>
-  <si>
-    <t>QUINTANA ROO</t>
   </si>
   <si>
     <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
@@ -487,7 +487,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -495,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -447,7 +447,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -519,7 +519,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -543,7 +543,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -447,7 +447,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -495,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -551,7 +551,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -495,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -495,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -543,7 +543,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -495,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -519,7 +519,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -495,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -543,7 +543,7 @@
         <v>14</v>
       </c>
       <c r="B14">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -58,13 +58,13 @@
     <t>PUEBLA</t>
   </si>
   <si>
+    <t>NAYARIT</t>
+  </si>
+  <si>
+    <t>MORELOS</t>
+  </si>
+  <si>
     <t>CAMPECHE</t>
-  </si>
-  <si>
-    <t>MORELOS</t>
-  </si>
-  <si>
-    <t>NAYARIT</t>
   </si>
   <si>
     <t>CHIAPAS</t>
@@ -495,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -559,7 +559,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -495,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -559,7 +559,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -40,10 +40,10 @@
     <t>QUINTANA ROO</t>
   </si>
   <si>
+    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
+  </si>
+  <si>
     <t>TABASCO</t>
-  </si>
-  <si>
-    <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
     <t>OAXACA</t>
@@ -463,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -495,7 +495,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -503,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>entidad</t>
   </si>
@@ -58,16 +58,13 @@
     <t>PUEBLA</t>
   </si>
   <si>
+    <t>MORELOS</t>
+  </si>
+  <si>
     <t>NAYARIT</t>
   </si>
   <si>
-    <t>MORELOS</t>
-  </si>
-  <si>
     <t>CAMPECHE</t>
-  </si>
-  <si>
-    <t>CHIAPAS</t>
   </si>
   <si>
     <t>SAN LUIS POTOSI</t>
@@ -431,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -578,14 +575,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -58,10 +58,10 @@
     <t>PUEBLA</t>
   </si>
   <si>
+    <t>NAYARIT</t>
+  </si>
+  <si>
     <t>MORELOS</t>
-  </si>
-  <si>
-    <t>NAYARIT</t>
   </si>
   <si>
     <t>CAMPECHE</t>
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -500,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -548,7 +548,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -548,7 +548,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -61,10 +61,10 @@
     <t>NAYARIT</t>
   </si>
   <si>
+    <t>CAMPECHE</t>
+  </si>
+  <si>
     <t>MORELOS</t>
-  </si>
-  <si>
-    <t>CAMPECHE</t>
   </si>
   <si>
     <t>SAN LUIS POTOSI</t>
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -444,7 +444,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -43,10 +43,10 @@
     <t>VERACRUZ DE IGNACIO DE LA LLAVE</t>
   </si>
   <si>
+    <t>OAXACA</t>
+  </si>
+  <si>
     <t>TABASCO</t>
-  </si>
-  <si>
-    <t>OAXACA</t>
   </si>
   <si>
     <t>BAJA CALIFORNIA SUR</t>
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -500,7 +500,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -508,7 +508,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -444,7 +444,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -444,7 +444,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -49,10 +49,10 @@
     <t>TABASCO</t>
   </si>
   <si>
+    <t>COLIMA</t>
+  </si>
+  <si>
     <t>BAJA CALIFORNIA SUR</t>
-  </si>
-  <si>
-    <t>COLIMA</t>
   </si>
   <si>
     <t>PUEBLA</t>
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -524,7 +524,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -444,7 +444,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -444,7 +444,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -49,10 +49,10 @@
     <t>TABASCO</t>
   </si>
   <si>
+    <t>BAJA CALIFORNIA SUR</t>
+  </si>
+  <si>
     <t>COLIMA</t>
-  </si>
-  <si>
-    <t>BAJA CALIFORNIA SUR</t>
   </si>
   <si>
     <t>PUEBLA</t>
@@ -516,7 +516,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -49,10 +49,10 @@
     <t>TABASCO</t>
   </si>
   <si>
+    <t>COLIMA</t>
+  </si>
+  <si>
     <t>BAJA CALIFORNIA SUR</t>
-  </si>
-  <si>
-    <t>COLIMA</t>
   </si>
   <si>
     <t>PUEBLA</t>
@@ -524,7 +524,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -444,7 +444,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>184</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -22,12 +22,12 @@
     <t>clues_faltantes</t>
   </si>
   <si>
+    <t>GUERRERO</t>
+  </si>
+  <si>
     <t>CIUDAD DE MEXICO</t>
   </si>
   <si>
-    <t>GUERRERO</t>
-  </si>
-  <si>
     <t>SONORA</t>
   </si>
   <si>
@@ -52,10 +52,10 @@
     <t>COLIMA</t>
   </si>
   <si>
+    <t>PUEBLA</t>
+  </si>
+  <si>
     <t>BAJA CALIFORNIA SUR</t>
-  </si>
-  <si>
-    <t>PUEBLA</t>
   </si>
   <si>
     <t>NAYARIT</t>
@@ -444,7 +444,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -452,7 +452,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -524,7 +524,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -556,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -452,7 +452,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -452,7 +452,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -460,7 +460,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -452,7 +452,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -452,7 +452,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -484,7 +484,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -452,7 +452,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>entidad</t>
   </si>
@@ -49,22 +49,19 @@
     <t>TABASCO</t>
   </si>
   <si>
+    <t>PUEBLA</t>
+  </si>
+  <si>
+    <t>BAJA CALIFORNIA SUR</t>
+  </si>
+  <si>
     <t>COLIMA</t>
   </si>
   <si>
-    <t>PUEBLA</t>
-  </si>
-  <si>
-    <t>BAJA CALIFORNIA SUR</t>
-  </si>
-  <si>
     <t>NAYARIT</t>
   </si>
   <si>
     <t>CAMPECHE</t>
-  </si>
-  <si>
-    <t>MORELOS</t>
   </si>
   <si>
     <t>SAN LUIS POTOSI</t>
@@ -428,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -452,7 +449,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -516,7 +513,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -532,7 +529,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -556,7 +553,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -564,14 +561,6 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18">
         <v>1</v>
       </c>
     </row>

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -449,7 +449,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -457,7 +457,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -521,7 +521,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -449,7 +449,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -473,7 +473,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -457,7 +457,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -457,7 +457,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -457,7 +457,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:2">

--- a/tabla_faltantes_por_estados.xlsx
+++ b/tabla_faltantes_por_estados.xlsx
@@ -545,7 +545,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:2">
